--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,116 +587,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F2">
+        <v>0.173</v>
+      </c>
       <c r="G2">
-        <v>0.3234681303909489</v>
+        <v>0.6505935400754578</v>
       </c>
       <c r="H2">
-        <v>0.3234681303909489</v>
+        <v>0.6505935400754578</v>
       </c>
       <c r="I2">
-        <v>0.5438781225495688</v>
+        <v>0.198684089445109</v>
       </c>
       <c r="J2">
-        <v>0.5402522683992383</v>
+        <v>0.1976335334990635</v>
       </c>
       <c r="K2">
-        <v>59.27</v>
+        <v>247.917</v>
       </c>
       <c r="L2">
-        <v>0.2655763414360928</v>
+        <v>1.140687402226926</v>
       </c>
       <c r="M2">
-        <v>125.7</v>
+        <v>222.0712</v>
       </c>
       <c r="N2">
-        <v>0.0373225176220479</v>
+        <v>0.03064365541632341</v>
       </c>
       <c r="O2">
-        <v>2.120803104437321</v>
+        <v>0.8957481737839679</v>
       </c>
       <c r="P2">
-        <v>125.7</v>
+        <v>98.77119999999999</v>
       </c>
       <c r="Q2">
-        <v>0.0373225176220479</v>
+        <v>0.01362946036161719</v>
       </c>
       <c r="R2">
-        <v>2.120803104437321</v>
+        <v>0.3984043046664811</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>123.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5552273324951638</v>
       </c>
       <c r="U2">
-        <v>48.834</v>
+        <v>36.334</v>
       </c>
       <c r="V2">
-        <v>0.01449966448333402</v>
+        <v>0.005013736927150818</v>
       </c>
       <c r="W2">
-        <v>-0.8831168831168832</v>
+        <v>-0.2826737451737452</v>
       </c>
       <c r="X2">
-        <v>0.04819851357868374</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y2">
-        <v>-0.931315396695567</v>
+        <v>-0.3610150888548556</v>
       </c>
       <c r="Z2">
-        <v>3.49891822400602</v>
-      </c>
-      <c r="AA2">
-        <v>-0.7755102040816327</v>
+        <v>0.6063514293924489</v>
       </c>
       <c r="AB2">
-        <v>0.04818912792889185</v>
-      </c>
-      <c r="AC2">
-        <v>-0.823683864808471</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AD2">
-        <v>2.059</v>
+        <v>21.318</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.059</v>
+        <v>21.318</v>
       </c>
       <c r="AG2">
-        <v>-46.775</v>
+        <v>-15.016</v>
       </c>
       <c r="AH2">
-        <v>0.000610979409786175</v>
+        <v>0.002933047595776015</v>
       </c>
       <c r="AI2">
-        <v>0.006304367129109398</v>
+        <v>0.05007340246867182</v>
       </c>
       <c r="AJ2">
-        <v>-0.01408391332559508</v>
+        <v>-0.002076363609211111</v>
       </c>
       <c r="AK2">
-        <v>-0.1683977462963296</v>
+        <v>-0.03856179105857457</v>
       </c>
       <c r="AL2">
-        <v>3.557</v>
+        <v>0.717</v>
       </c>
       <c r="AM2">
-        <v>3.184</v>
+        <v>-24.605</v>
       </c>
       <c r="AN2">
-        <v>0.01579229943242828</v>
+        <v>0.232983606557377</v>
       </c>
       <c r="AO2">
-        <v>34.12426201855496</v>
+        <v>60.22594142259415</v>
       </c>
       <c r="AP2">
-        <v>-0.358759012118423</v>
+        <v>-0.1641092896174863</v>
       </c>
       <c r="AQ2">
-        <v>38.12185929648241</v>
+        <v>-1.755009144482829</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Patria Investments Limited (NasdaqGS:PAX)</t>
+          <t>Phoenician International Limited (NSX:PHI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,115 +713,85 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3342379014020805</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.3342379014020805</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5712347354138398</v>
+        <v>0.2521505376344086</v>
       </c>
       <c r="J3">
-        <v>0.5712347354138398</v>
+        <v>0.2521505376344086</v>
       </c>
       <c r="K3">
-        <v>124.8</v>
+        <v>52.4</v>
       </c>
       <c r="L3">
-        <v>0.5644504748982361</v>
+        <v>28.17204301075268</v>
       </c>
       <c r="M3">
-        <v>125.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05699129488574538</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.007211538461539</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>125.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.05699129488574538</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.007211538461539</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>44.3</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.02008523757707653</v>
-      </c>
-      <c r="W3">
-        <v>1.388209121245829</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.04819851357868374</v>
-      </c>
-      <c r="Y3">
-        <v>1.340010607667145</v>
-      </c>
-      <c r="Z3">
-        <v>4.263401465483995</v>
-      </c>
-      <c r="AA3">
-        <v>2.435403008098727</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AB3">
-        <v>0.04818912792889185</v>
-      </c>
-      <c r="AC3">
-        <v>2.387213880169836</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AD3">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-42.58</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.0007792254861098527</v>
-      </c>
-      <c r="AI3">
-        <v>0.004411161263848994</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01968543980175865</v>
-      </c>
-      <c r="AK3">
-        <v>-0.1231988889531856</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.03</v>
+        <v>0.495</v>
       </c>
       <c r="AM3">
-        <v>1.03</v>
-      </c>
-      <c r="AN3">
-        <v>0.01295180722891566</v>
+        <v>0.495</v>
       </c>
       <c r="AO3">
-        <v>122.621359223301</v>
-      </c>
-      <c r="AP3">
-        <v>-0.3206325301204819</v>
+        <v>0.9474747474747475</v>
       </c>
       <c r="AQ3">
-        <v>122.621359223301</v>
+        <v>0.9474747474747475</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +802,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mineral &amp; Financial Investments Limited (AIM:MAFL)</t>
+          <t>Patria Investments Limited (NasdaqGS:PAX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,101 +810,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F4">
+        <v>0.173</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.6610565684899485</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.6610565684899485</v>
       </c>
       <c r="I4">
-        <v>0.7712765957446809</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="J4">
-        <v>0.7455673758865249</v>
+        <v>0.3135615536537196</v>
       </c>
       <c r="K4">
-        <v>1.33</v>
+        <v>59.6</v>
       </c>
       <c r="L4">
-        <v>0.7074468085106383</v>
+        <v>0.2786348761103319</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>98.77119999999999</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04817167381974248</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.657234899328859</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>98.77119999999999</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04817167381974248</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>1.657234899328859</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1.18</v>
+        <v>24.4</v>
       </c>
       <c r="V4">
-        <v>0.2213883677298311</v>
+        <v>0.01190011705033164</v>
       </c>
       <c r="W4">
-        <v>0.196165191740413</v>
+        <v>0.1535291087068522</v>
       </c>
       <c r="X4">
-        <v>0.04825959256344974</v>
+        <v>0.07861325791535917</v>
       </c>
       <c r="Y4">
-        <v>0.1479055991769632</v>
+        <v>0.07491585079149299</v>
       </c>
       <c r="Z4">
-        <v>0.2913825170489771</v>
+        <v>0.6188877958451479</v>
       </c>
       <c r="AA4">
-        <v>0.2172452986154164</v>
+        <v>0.1940594188025306</v>
       </c>
       <c r="AB4">
-        <v>0.04822787794360506</v>
+        <v>0.07844948698835098</v>
       </c>
       <c r="AC4">
-        <v>0.1690174206718114</v>
+        <v>0.1156099318141796</v>
       </c>
       <c r="AD4">
-        <v>0.014</v>
+        <v>14.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.014</v>
+        <v>14.1</v>
       </c>
       <c r="AG4">
-        <v>-1.166</v>
+        <v>-10.3</v>
       </c>
       <c r="AH4">
-        <v>0.002619760479041916</v>
+        <v>0.006829740857350448</v>
       </c>
       <c r="AI4">
-        <v>0.001572327044025157</v>
+        <v>0.02661884085331319</v>
       </c>
       <c r="AJ4">
-        <v>-0.2800192122958693</v>
+        <v>-0.005048772119013773</v>
       </c>
       <c r="AK4">
-        <v>-0.1509580528223718</v>
+        <v>-0.02038393033841282</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-5.778</v>
+      </c>
+      <c r="AN4">
+        <v>0.1540983606557377</v>
+      </c>
+      <c r="AO4">
+        <v>341.8918918918919</v>
+      </c>
+      <c r="AP4">
+        <v>-0.1125683060109289</v>
+      </c>
+      <c r="AQ4">
+        <v>-13.13603322949118</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Burgundy Technology Acquisition Corporation (NasdaqCM:BTAQ)</t>
+          <t>Mineral &amp; Financial Investments Limited (AIM:MAFL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,8 +941,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.589240506329114</v>
+      </c>
+      <c r="J5">
+        <v>0.589240506329114</v>
+      </c>
       <c r="K5">
-        <v>-6.22</v>
+        <v>1.09</v>
+      </c>
+      <c r="L5">
+        <v>0.689873417721519</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -966,7 +966,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -975,70 +975,67 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.074</v>
+        <v>0.584</v>
       </c>
       <c r="V5">
-        <v>0.000167307257517522</v>
+        <v>0.07594278283485045</v>
       </c>
       <c r="W5">
-        <v>-1.244</v>
+        <v>0.1226096737907762</v>
       </c>
       <c r="X5">
-        <v>0.04817504038011907</v>
+        <v>0.07840304668815506</v>
       </c>
       <c r="Y5">
-        <v>-1.292175040380119</v>
+        <v>0.04420662710262109</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.2045572242361471</v>
       </c>
       <c r="AA5">
-        <v>-0.7755102040816327</v>
+        <v>0.1205334023821854</v>
       </c>
       <c r="AB5">
-        <v>0.04817366072683826</v>
+        <v>0.07838393133259615</v>
       </c>
       <c r="AC5">
-        <v>-0.823683864808471</v>
+        <v>0.04214947104958926</v>
       </c>
       <c r="AD5">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="AG5">
-        <v>-0.043</v>
+        <v>-0.572</v>
       </c>
       <c r="AH5">
-        <v>7.008326343846576e-05</v>
+        <v>0.001558036873539341</v>
       </c>
       <c r="AI5">
-        <v>-0.001207682418481437</v>
+        <v>0.001322751322751323</v>
       </c>
       <c r="AJ5">
-        <v>-9.722853453987161e-05</v>
+        <v>-0.08035965158752457</v>
       </c>
       <c r="AK5">
-        <v>0.001670356990249777</v>
+        <v>-0.06738925541941564</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.031</v>
-      </c>
-      <c r="AQ5">
-        <v>85.80645161290323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1049,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIQ Limited (LSE:AIQ)</t>
+          <t>Finnovate Acquisition Corp. (NasdaqGM:FNVT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1057,23 +1054,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-8.769230769230768</v>
-      </c>
-      <c r="H6">
-        <v>-8.769230769230768</v>
-      </c>
-      <c r="I6">
-        <v>-12.87179487179487</v>
-      </c>
-      <c r="J6">
-        <v>-12.87179487179487</v>
-      </c>
       <c r="K6">
-        <v>-5.44</v>
-      </c>
-      <c r="L6">
-        <v>-27.8974358974359</v>
+        <v>-0.373</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1097,73 +1079,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.41</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="V6">
-        <v>0.1467221644120708</v>
+        <v>0.0025</v>
       </c>
       <c r="W6">
-        <v>-0.8831168831168832</v>
+        <v>-26.64285714285714</v>
       </c>
       <c r="X6">
-        <v>0.04918452053961156</v>
+        <v>0.07842120725676796</v>
       </c>
       <c r="Y6">
-        <v>-0.9323014036564947</v>
+        <v>-26.72127835011391</v>
       </c>
       <c r="Z6">
-        <v>0.09549461312438784</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-1.229187071498531</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04879770003047976</v>
+        <v>0.07837326026986906</v>
       </c>
       <c r="AC6">
-        <v>-1.27798477152901</v>
+        <v>-0.07837326026986906</v>
       </c>
       <c r="AD6">
-        <v>0.294</v>
+        <v>0.45</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.294</v>
+        <v>0.45</v>
       </c>
       <c r="AG6">
-        <v>-1.116</v>
+        <v>-0.107</v>
       </c>
       <c r="AH6">
-        <v>0.02968497576736672</v>
+        <v>0.002015677491601344</v>
       </c>
       <c r="AI6">
-        <v>0.1788321167883211</v>
+        <v>0.5717916137229987</v>
       </c>
       <c r="AJ6">
-        <v>-0.1313868613138686</v>
+        <v>-0.0004804820986739594</v>
       </c>
       <c r="AK6">
-        <v>-4.769230769230765</v>
+        <v>-0.465217391304348</v>
       </c>
       <c r="AL6">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.011</v>
-      </c>
-      <c r="AN6">
-        <v>-0.1214876033057851</v>
-      </c>
-      <c r="AO6">
-        <v>-147.6470588235294</v>
-      </c>
-      <c r="AP6">
-        <v>0.4611570247933884</v>
+        <v>-1.06</v>
       </c>
       <c r="AQ6">
-        <v>-228.1818181818181</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1174,7 +1147,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vy Global Growth (NYSE:VYGG)</t>
+          <t>Oxbridge Acquisition Corp. (NasdaqCM:OXAC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1183,7 +1156,7 @@
         </is>
       </c>
       <c r="K7">
-        <v>-55.2</v>
+        <v>-1.14</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1207,16 +1180,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.87</v>
+        <v>0.279</v>
       </c>
       <c r="V7">
-        <v>0.00265210608424337</v>
+        <v>0.001842800528401585</v>
+      </c>
+      <c r="W7">
+        <v>-0.228</v>
       </c>
       <c r="X7">
-        <v>0.04817272237335087</v>
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y7">
+        <v>-0.3063413436811104</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-0.06493207460280911</v>
       </c>
       <c r="AB7">
-        <v>0.04817272237335087</v>
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1432734182839195</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1228,31 +1216,1619 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-1.87</v>
+        <v>-0.279</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AI7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.002659158454559675</v>
+        <v>-0.001846202711734306</v>
       </c>
       <c r="AK7">
-        <v>0.03734771320151788</v>
+        <v>-0.05909764880321966</v>
       </c>
       <c r="AL7">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>2.174</v>
-      </c>
-      <c r="AO7">
-        <v>-0.4780876494023905</v>
+        <v>-0.495</v>
       </c>
       <c r="AQ7">
-        <v>-0.5519779208831647</v>
+        <v>0.5696969696969697</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patria Latin American Opportunity Acquisition Corp. (NasdaqGM:PLAO)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>5.07</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.002714429868819374</v>
+      </c>
+      <c r="W8">
+        <v>-211.25</v>
+      </c>
+      <c r="X8">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y8">
+        <v>-211.3283413436811</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>-5.628571428571428</v>
+      </c>
+      <c r="AB8">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC8">
+        <v>-5.706912772252538</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-0.8070000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.002721818053040038</v>
+      </c>
+      <c r="AK8">
+        <v>0.06504392681550737</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Generation Asia I Acquisition Limited (NYSE:GAQ)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>6.9</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.327</v>
+      </c>
+      <c r="V9">
+        <v>0.001098421229425596</v>
+      </c>
+      <c r="W9">
+        <v>-575</v>
+      </c>
+      <c r="X9">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y9">
+        <v>-575.0783413436811</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>-7.108108108108108</v>
+      </c>
+      <c r="AB9">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC9">
+        <v>-7.186449451789218</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-0.327</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>-0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.001099629085357447</v>
+      </c>
+      <c r="AK9">
+        <v>0.03476134793239077</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1.54</v>
+      </c>
+      <c r="AQ9">
+        <v>0.5123376623376623</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ahren Acquisition Corp. (NasdaqGM:AHRN)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>7.9</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0.912</v>
+      </c>
+      <c r="V10">
+        <v>0.002376237623762376</v>
+      </c>
+      <c r="W10">
+        <v>1128.571428571429</v>
+      </c>
+      <c r="X10">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y10">
+        <v>1128.493087227748</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>-19.81818181818182</v>
+      </c>
+      <c r="AB10">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC10">
+        <v>-19.89652316186293</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>-0.912</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-0</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.002381897578404128</v>
+      </c>
+      <c r="AK10">
+        <v>0.0641711229946524</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Target Global Acquisition I Corp. (NasdaqGM:TGAA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>0.03</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.308</v>
+      </c>
+      <c r="V11">
+        <v>0.001119592875318066</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+      <c r="X11">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y11">
+        <v>1.92165865631889</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>-29.76190476190477</v>
+      </c>
+      <c r="AB11">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC11">
+        <v>-29.84024610558588</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>-0.308</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-0</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.001120847768493988</v>
+      </c>
+      <c r="AK11">
+        <v>0.03812824956672444</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-1.19</v>
+      </c>
+      <c r="AQ11">
+        <v>1.050420168067227</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Blockchain Coinvestors Acquisition Corp. I (NasdaqGM:BCSA)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>7.67</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.0002008981328291184</v>
+      </c>
+      <c r="W12">
+        <v>383.5</v>
+      </c>
+      <c r="X12">
+        <v>0.07835723124534058</v>
+      </c>
+      <c r="Y12">
+        <v>383.4216427687547</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>-35.84905660377358</v>
+      </c>
+      <c r="AB12">
+        <v>0.0783523220392105</v>
+      </c>
+      <c r="AC12">
+        <v>-35.92740892581278</v>
+      </c>
+      <c r="AD12">
+        <v>0.17</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0.17</v>
+      </c>
+      <c r="AG12">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.0004016348902591726</v>
+      </c>
+      <c r="AI12">
+        <v>-0.01131071190951431</v>
+      </c>
+      <c r="AJ12">
+        <v>0.0002008577808759762</v>
+      </c>
+      <c r="AK12">
+        <v>-0.005623552762156799</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1.68</v>
+      </c>
+      <c r="AQ12">
+        <v>2.261904761904762</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Healthcare AI Acquisition Corp. (NasdaqGM:HAIA)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>21.4</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0.465</v>
+      </c>
+      <c r="V13">
+        <v>0.001681735985533454</v>
+      </c>
+      <c r="W13">
+        <v>2675</v>
+      </c>
+      <c r="X13">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y13">
+        <v>2674.921658656318</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>-43.11111111111111</v>
+      </c>
+      <c r="AB13">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AC13">
+        <v>-43.18945245479222</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>-0.465</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-0</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.001684568985817016</v>
+      </c>
+      <c r="AK13">
+        <v>0.04447632711621234</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1.28</v>
+      </c>
+      <c r="AQ13">
+        <v>3.03125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Investcorp Europe Acquisition Corp I (NasdaqGM:IVCB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>25.1</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0.578</v>
+      </c>
+      <c r="V14">
+        <v>0.00130121566861774</v>
+      </c>
+      <c r="X14">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AB14">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-0.578</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-0</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.001302911036873735</v>
+      </c>
+      <c r="AK14">
+        <v>0.03992264124879127</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-2.1</v>
+      </c>
+      <c r="AQ14">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Levere Holdings Corp. (NasdaqCM:LVRA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>11.4</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0.513</v>
+      </c>
+      <c r="V15">
+        <v>0.001500877706260971</v>
+      </c>
+      <c r="W15">
+        <v>-0.5507246376811594</v>
+      </c>
+      <c r="X15">
+        <v>0.07845240187284203</v>
+      </c>
+      <c r="Y15">
+        <v>-0.6291770395540015</v>
+      </c>
+      <c r="AB15">
+        <v>0.07841790106044128</v>
+      </c>
+      <c r="AD15">
+        <v>0.96</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0.96</v>
+      </c>
+      <c r="AG15">
+        <v>0.447</v>
+      </c>
+      <c r="AH15">
+        <v>0.002800793558174816</v>
+      </c>
+      <c r="AI15">
+        <v>-0.09958506224066389</v>
+      </c>
+      <c r="AJ15">
+        <v>0.001306074267999427</v>
+      </c>
+      <c r="AK15">
+        <v>-0.04402639613907219</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1.64</v>
+      </c>
+      <c r="AQ15">
+        <v>0.9024390243902439</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rocket Internet Growth Opportunities Corp. (NYSE:RKTA)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>-0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0.421</v>
+      </c>
+      <c r="V16">
+        <v>0.001248887570453871</v>
+      </c>
+      <c r="W16">
+        <v>-0.539080459770115</v>
+      </c>
+      <c r="X16">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y16">
+        <v>-0.6174218034512253</v>
+      </c>
+      <c r="AB16">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>-0.421</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>-0</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.0012504492409684</v>
+      </c>
+      <c r="AK16">
+        <v>0.03963845212315225</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1.62</v>
+      </c>
+      <c r="AQ16">
+        <v>0.7469135802469135</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Investcorp India Acquisition Corp (NasdaqGM:IVCA)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>3.57</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0.858</v>
+      </c>
+      <c r="V17">
+        <v>0.002565789473684211</v>
+      </c>
+      <c r="X17">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AB17">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>-0.858</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-0</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.00257238968405778</v>
+      </c>
+      <c r="AK17">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1.47</v>
+      </c>
+      <c r="AQ17">
+        <v>0.5394557823129252</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Valor Latitude Acquisition Corp. (NasdaqCM:VLAT)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>9.56</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0.2</v>
+      </c>
+      <c r="V18">
+        <v>0.0006915629322268327</v>
+      </c>
+      <c r="W18">
+        <v>-0.5590643274853802</v>
+      </c>
+      <c r="X18">
+        <v>0.07835747742438279</v>
+      </c>
+      <c r="Y18">
+        <v>-0.637421804909763</v>
+      </c>
+      <c r="AB18">
+        <v>0.07835249208034173</v>
+      </c>
+      <c r="AD18">
+        <v>0.118</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0.118</v>
+      </c>
+      <c r="AG18">
+        <v>-0.08200000000000002</v>
+      </c>
+      <c r="AH18">
+        <v>0.0004078557158559094</v>
+      </c>
+      <c r="AI18">
+        <v>-0.01271277741865977</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.0002836212204013587</v>
+      </c>
+      <c r="AK18">
+        <v>0.008647964564437883</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1.38</v>
+      </c>
+      <c r="AQ18">
+        <v>0.7536231884057972</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>World Quantum Growth Acquisition Corp. (NYSE:WQGA)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>13.8</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.203</v>
+      </c>
+      <c r="V19">
+        <v>0.0007813702848344881</v>
+      </c>
+      <c r="W19">
+        <v>-0.7709497206703911</v>
+      </c>
+      <c r="X19">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="Y19">
+        <v>-0.8492910643515015</v>
+      </c>
+      <c r="AB19">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>-0.203</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>-0</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.0007819813017870006</v>
+      </c>
+      <c r="AK19">
+        <v>0.02523933855526545</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1.26</v>
+      </c>
+      <c r="AQ19">
+        <v>1.007936507936508</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TB SA Acquisition Corp (NasdaqCM:TBSA)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>4.37</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0.047</v>
+      </c>
+      <c r="V20">
+        <v>0.0001865079365079365</v>
+      </c>
+      <c r="W20">
+        <v>-0.7105691056910569</v>
+      </c>
+      <c r="X20">
+        <v>0.07842262310978824</v>
+      </c>
+      <c r="Y20">
+        <v>-0.7889917288008451</v>
+      </c>
+      <c r="AB20">
+        <v>0.0783738249390547</v>
+      </c>
+      <c r="AD20">
+        <v>0.518</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0.518</v>
+      </c>
+      <c r="AG20">
+        <v>0.471</v>
+      </c>
+      <c r="AH20">
+        <v>0.002051338914453623</v>
+      </c>
+      <c r="AI20">
+        <v>-0.2070343725019984</v>
+      </c>
+      <c r="AJ20">
+        <v>0.001865560797081645</v>
+      </c>
+      <c r="AK20">
+        <v>-0.1847783444488035</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1.2</v>
+      </c>
+      <c r="AQ20">
+        <v>2.933333333333334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Blue Whale Acquisition Corp I (NasdaqCM:BWC)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>4.35</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>2.13</v>
+      </c>
+      <c r="V21">
+        <v>0.008537074148296592</v>
+      </c>
+      <c r="W21">
+        <v>-0.2939189189189189</v>
+      </c>
+      <c r="X21">
+        <v>0.07881362105253209</v>
+      </c>
+      <c r="Y21">
+        <v>-0.3727325399714509</v>
+      </c>
+      <c r="AB21">
+        <v>0.07852823309591374</v>
+      </c>
+      <c r="AD21">
+        <v>2.98</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>2.98</v>
+      </c>
+      <c r="AG21">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="AH21">
+        <v>0.01180291508238276</v>
+      </c>
+      <c r="AI21">
+        <v>-0.3539192399049881</v>
+      </c>
+      <c r="AJ21">
+        <v>0.003395246654683444</v>
+      </c>
+      <c r="AK21">
+        <v>-0.08056872037914692</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JATT Acquisition Corp (NYSE:JATT)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K22">
+        <v>5.36</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>-0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.074</v>
+      </c>
+      <c r="V22">
+        <v>0.0004202157864849518</v>
+      </c>
+      <c r="W22">
+        <v>-0.5203883495145631</v>
+      </c>
+      <c r="X22">
+        <v>0.07840870542503053</v>
+      </c>
+      <c r="Y22">
+        <v>-0.5987970549395937</v>
+      </c>
+      <c r="AB22">
+        <v>0.07836827254898784</v>
+      </c>
+      <c r="AD22">
+        <v>0.3</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0.3</v>
+      </c>
+      <c r="AG22">
+        <v>0.226</v>
+      </c>
+      <c r="AH22">
+        <v>0.001700680272108843</v>
+      </c>
+      <c r="AI22">
+        <v>-0.04405286343612334</v>
+      </c>
+      <c r="AJ22">
+        <v>0.001281716819981171</v>
+      </c>
+      <c r="AK22">
+        <v>-0.03282975014526437</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-0.9</v>
+      </c>
+      <c r="AQ22">
+        <v>3.022222222222222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aries I Acquisition Corporation (NasdaqCM:RAM)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K23">
+        <v>2.85</v>
+      </c>
+      <c r="M23">
+        <v>123.3</v>
+      </c>
+      <c r="N23">
+        <v>2.03801652892562</v>
+      </c>
+      <c r="O23">
+        <v>43.26315789473684</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>-0</v>
+      </c>
+      <c r="S23">
+        <v>123.3</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>0.026</v>
+      </c>
+      <c r="V23">
+        <v>0.0004297520661157025</v>
+      </c>
+      <c r="W23">
+        <v>-0.2714285714285715</v>
+      </c>
+      <c r="X23">
+        <v>0.07945895851903931</v>
+      </c>
+      <c r="Y23">
+        <v>-0.3508875299476107</v>
+      </c>
+      <c r="AB23">
+        <v>0.07877658621564496</v>
+      </c>
+      <c r="AD23">
+        <v>1.71</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>1.71</v>
+      </c>
+      <c r="AG23">
+        <v>1.684</v>
+      </c>
+      <c r="AH23">
+        <v>0.02748754219578846</v>
+      </c>
+      <c r="AI23">
+        <v>-0.3461538461538461</v>
+      </c>
+      <c r="AJ23">
+        <v>0.02708092113727004</v>
+      </c>
+      <c r="AK23">
+        <v>-0.3391059202577527</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-0.507</v>
+      </c>
+      <c r="AQ23">
+        <v>6.193293885601578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vertex Technology Acquisition Corporation Ltd. (SGX:VT1)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K24">
+        <v>-2.37</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>2.56</v>
+      </c>
+      <c r="V24">
+        <v>0.1267326732673267</v>
+      </c>
+      <c r="X24">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AB24">
+        <v>0.0783413436811104</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>-2.56</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.145124716553288</v>
+      </c>
+      <c r="AK24">
+        <v>-0.1264822134387352</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ24"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,113 +587,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.627</v>
+      </c>
+      <c r="E2">
+        <v>1.115</v>
+      </c>
       <c r="F2">
-        <v>0.173</v>
+        <v>0.186</v>
       </c>
       <c r="G2">
-        <v>0.6505935400754578</v>
+        <v>0.4051701908200103</v>
       </c>
       <c r="H2">
-        <v>0.6505935400754578</v>
+        <v>0.4051701908200103</v>
       </c>
       <c r="I2">
-        <v>0.198684089445109</v>
+        <v>0.3448942753996905</v>
       </c>
       <c r="J2">
-        <v>0.1976335334990635</v>
+        <v>0.3389855321005455</v>
       </c>
       <c r="K2">
-        <v>247.917</v>
+        <v>167.56</v>
       </c>
       <c r="L2">
-        <v>1.140687402226926</v>
+        <v>0.5400979886539453</v>
       </c>
       <c r="M2">
-        <v>222.0712</v>
+        <v>1789.5</v>
       </c>
       <c r="N2">
-        <v>0.03064365541632341</v>
+        <v>0.4706894238887706</v>
       </c>
       <c r="O2">
-        <v>0.8957481737839679</v>
+        <v>10.67975650513249</v>
       </c>
       <c r="P2">
-        <v>98.77119999999999</v>
+        <v>140.9</v>
       </c>
       <c r="Q2">
-        <v>0.01362946036161719</v>
+        <v>0.03706070959817143</v>
       </c>
       <c r="R2">
-        <v>0.3984043046664811</v>
+        <v>0.8408928145142038</v>
       </c>
       <c r="S2">
-        <v>123.3</v>
+        <v>1648.6</v>
       </c>
       <c r="T2">
-        <v>0.5552273324951638</v>
+        <v>0.9212629226040794</v>
       </c>
       <c r="U2">
-        <v>36.334</v>
+        <v>19.841</v>
       </c>
       <c r="V2">
-        <v>0.005013736927150818</v>
+        <v>0.005218747616304608</v>
       </c>
       <c r="W2">
-        <v>-0.2826737451737452</v>
+        <v>-0.1872694556905083</v>
       </c>
       <c r="X2">
-        <v>0.0783413436811104</v>
+        <v>0.06696743882627161</v>
       </c>
       <c r="Y2">
-        <v>-0.3610150888548556</v>
+        <v>-0.2542368945167799</v>
       </c>
       <c r="Z2">
-        <v>0.6063514293924489</v>
+        <v>1.164048957293691</v>
       </c>
       <c r="AB2">
-        <v>0.0783413436811104</v>
+        <v>0.06686965710829618</v>
       </c>
       <c r="AD2">
-        <v>21.318</v>
+        <v>31.429</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.318</v>
+        <v>31.429</v>
       </c>
       <c r="AG2">
-        <v>-15.016</v>
+        <v>11.588</v>
       </c>
       <c r="AH2">
-        <v>0.002933047595776015</v>
+        <v>0.008198942999228602</v>
       </c>
       <c r="AI2">
-        <v>0.05007340246867182</v>
+        <v>0.07663572367346243</v>
       </c>
       <c r="AJ2">
-        <v>-0.002076363609211111</v>
+        <v>0.00303871184630852</v>
       </c>
       <c r="AK2">
-        <v>-0.03856179105857457</v>
+        <v>0.02969241649328154</v>
       </c>
       <c r="AL2">
-        <v>0.717</v>
+        <v>2.9</v>
       </c>
       <c r="AM2">
-        <v>-24.605</v>
+        <v>-54.2</v>
       </c>
       <c r="AN2">
-        <v>0.232983606557377</v>
+        <v>0.2034239482200647</v>
       </c>
       <c r="AO2">
-        <v>60.22594142259415</v>
+        <v>36.89655172413793</v>
       </c>
       <c r="AP2">
-        <v>-0.1641092896174863</v>
+        <v>0.07500323624595467</v>
       </c>
       <c r="AQ2">
-        <v>-1.755009144482829</v>
+        <v>-1.974169741697417</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phoenician International Limited (NSX:PHI)</t>
+          <t>Patria Investments Limited (NasdaqGS:PAX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,86 +718,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.186</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4091796875</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4091796875</v>
       </c>
       <c r="I3">
-        <v>0.2521505376344086</v>
+        <v>0.4309895833333334</v>
       </c>
       <c r="J3">
-        <v>0.2521505376344086</v>
+        <v>0.4309895833333334</v>
       </c>
       <c r="K3">
-        <v>52.4</v>
+        <v>117.9</v>
       </c>
       <c r="L3">
-        <v>28.17204301075268</v>
+        <v>0.3837890625000001</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>206.1</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.09027595269382392</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.748091603053435</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>140.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06171703898379326</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.195080576759966</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>65.20000000000002</v>
+      </c>
+      <c r="T3">
+        <v>0.3163512857836002</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.007665352606219886</v>
+      </c>
+      <c r="W3">
+        <v>0.2282229965156795</v>
       </c>
       <c r="X3">
-        <v>0.0783413436811104</v>
+        <v>0.06697977615753684</v>
+      </c>
+      <c r="Y3">
+        <v>0.1612432203581426</v>
+      </c>
+      <c r="Z3">
+        <v>1.191621411947245</v>
+      </c>
+      <c r="AA3">
+        <v>0.5135764158262217</v>
       </c>
       <c r="AB3">
-        <v>0.0783413436811104</v>
+        <v>0.06687521626624278</v>
+      </c>
+      <c r="AC3">
+        <v>0.4467011995599789</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.006786739754633255</v>
+      </c>
+      <c r="AI3">
+        <v>0.03190184049079754</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.0008329314804261104</v>
+      </c>
+      <c r="AK3">
+        <v>-0.004029692470837753</v>
       </c>
       <c r="AL3">
-        <v>0.495</v>
+        <v>1.47</v>
       </c>
       <c r="AM3">
-        <v>0.495</v>
+        <v>1.47</v>
+      </c>
+      <c r="AN3">
+        <v>0.1009708737864078</v>
       </c>
       <c r="AO3">
-        <v>0.9474747474747475</v>
+        <v>90.06802721088435</v>
+      </c>
+      <c r="AP3">
+        <v>-0.01229773462783172</v>
       </c>
       <c r="AQ3">
-        <v>0.9474747474747475</v>
+        <v>90.06802721088435</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patria Investments Limited (NasdaqGS:PAX)</t>
+          <t>Mineral &amp; Financial Investments Limited (AIM:MAFL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -810,119 +849,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F4">
-        <v>0.173</v>
+      <c r="D4">
+        <v>0.627</v>
+      </c>
+      <c r="E4">
+        <v>1.115</v>
       </c>
       <c r="G4">
-        <v>0.6610565684899485</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.6610565684899485</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.3548387096774194</v>
+        <v>0.756578947368421</v>
       </c>
       <c r="J4">
-        <v>0.3135615536537196</v>
+        <v>0.7440953947368421</v>
       </c>
       <c r="K4">
-        <v>59.6</v>
+        <v>1.97</v>
       </c>
       <c r="L4">
-        <v>0.2786348761103319</v>
+        <v>0.6480263157894737</v>
       </c>
       <c r="M4">
-        <v>98.77119999999999</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04817167381974248</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.657234899328859</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>98.77119999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04817167381974248</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.657234899328859</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>24.4</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0.01190011705033164</v>
+        <v>0.1781305114638448</v>
       </c>
       <c r="W4">
-        <v>0.1535291087068522</v>
+        <v>0.217439293598234</v>
       </c>
       <c r="X4">
-        <v>0.07861325791535917</v>
+        <v>0.06685269857714116</v>
       </c>
       <c r="Y4">
-        <v>0.07491585079149299</v>
+        <v>0.1505865950210928</v>
       </c>
       <c r="Z4">
-        <v>0.6188877958451479</v>
+        <v>0.3581526861451461</v>
       </c>
       <c r="AA4">
-        <v>0.1940594188025306</v>
+        <v>0.2664997643732328</v>
       </c>
       <c r="AB4">
-        <v>0.07844948698835098</v>
+        <v>0.06683714702633549</v>
       </c>
       <c r="AC4">
-        <v>0.1156099318141796</v>
+        <v>0.1996626173468973</v>
       </c>
       <c r="AD4">
-        <v>14.1</v>
+        <v>0.013</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.1</v>
+        <v>0.013</v>
       </c>
       <c r="AG4">
-        <v>-10.3</v>
+        <v>-0.997</v>
       </c>
       <c r="AH4">
-        <v>0.006829740857350448</v>
+        <v>0.002287524194967447</v>
       </c>
       <c r="AI4">
-        <v>0.02661884085331319</v>
+        <v>0.001082160992258387</v>
       </c>
       <c r="AJ4">
-        <v>-0.005048772119013773</v>
+        <v>-0.213353306227263</v>
       </c>
       <c r="AK4">
-        <v>-0.02038393033841282</v>
+        <v>-0.09061165136780878</v>
       </c>
       <c r="AL4">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-5.778</v>
-      </c>
-      <c r="AN4">
-        <v>0.1540983606557377</v>
-      </c>
-      <c r="AO4">
-        <v>341.8918918918919</v>
-      </c>
-      <c r="AP4">
-        <v>-0.1125683060109289</v>
-      </c>
-      <c r="AQ4">
-        <v>-13.13603322949118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mineral &amp; Financial Investments Limited (AIM:MAFL)</t>
+          <t>Finnovate Acquisition Corp. (NasdaqGM:FNVT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -941,32 +968,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.589240506329114</v>
-      </c>
-      <c r="J5">
-        <v>0.589240506329114</v>
-      </c>
       <c r="K5">
-        <v>1.09</v>
-      </c>
-      <c r="L5">
-        <v>0.689873417721519</v>
+        <v>3.14</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>132.6</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>1.318091451292247</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>42.22929936305732</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -978,64 +990,70 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>132.6</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0.584</v>
+        <v>0.001</v>
       </c>
       <c r="V5">
-        <v>0.07594278283485045</v>
+        <v>9.940357852882704e-06</v>
       </c>
       <c r="W5">
-        <v>0.1226096737907762</v>
+        <v>9.317507418397627</v>
       </c>
       <c r="X5">
-        <v>0.07840304668815506</v>
+        <v>0.06692763533923096</v>
       </c>
       <c r="Y5">
-        <v>0.04420662710262109</v>
+        <v>9.250579783058395</v>
       </c>
       <c r="Z5">
-        <v>0.2045572242361471</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.1205334023821854</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07838393133259615</v>
+        <v>0.06685169885549978</v>
       </c>
       <c r="AC5">
-        <v>0.04214947104958926</v>
+        <v>-0.06685169885549978</v>
       </c>
       <c r="AD5">
-        <v>0.012</v>
+        <v>0.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.012</v>
+        <v>0.5</v>
       </c>
       <c r="AG5">
-        <v>-0.572</v>
+        <v>0.499</v>
       </c>
       <c r="AH5">
-        <v>0.001558036873539341</v>
+        <v>0.004945598417408507</v>
       </c>
       <c r="AI5">
-        <v>0.001322751322751323</v>
+        <v>-0.3355704697986577</v>
       </c>
       <c r="AJ5">
-        <v>-0.08035965158752457</v>
+        <v>0.004935756041108221</v>
       </c>
       <c r="AK5">
-        <v>-0.06738925541941564</v>
+        <v>-0.3346747149564051</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-5.42</v>
+      </c>
+      <c r="AQ5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finnovate Acquisition Corp. (NasdaqGM:FNVT)</t>
+          <t>Investcorp Europe Acquisition Corp I (NasdaqGM:IVCB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1055,16 +1073,16 @@
         </is>
       </c>
       <c r="K6">
-        <v>-0.373</v>
+        <v>-4.54</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>161.6</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.5307060755336617</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-35.59471365638766</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1076,67 +1094,61 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>161.6</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0.5570000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="V6">
-        <v>0.0025</v>
+        <v>0.0001018062397372742</v>
       </c>
       <c r="W6">
-        <v>-26.64285714285714</v>
+        <v>0.3266187050359712</v>
       </c>
       <c r="X6">
-        <v>0.07842120725676796</v>
+        <v>0.06709368961905998</v>
       </c>
       <c r="Y6">
-        <v>-26.72127835011391</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
+        <v>0.2595250154169113</v>
       </c>
       <c r="AB6">
-        <v>0.07837326026986906</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07837326026986906</v>
+        <v>0.0669262938504819</v>
       </c>
       <c r="AD6">
-        <v>0.45</v>
+        <v>3.32</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.45</v>
+        <v>3.32</v>
       </c>
       <c r="AG6">
-        <v>-0.107</v>
+        <v>3.289</v>
       </c>
       <c r="AH6">
-        <v>0.002015677491601344</v>
+        <v>0.01078552400753687</v>
       </c>
       <c r="AI6">
-        <v>0.5717916137229987</v>
+        <v>-0.113776559287183</v>
       </c>
       <c r="AJ6">
-        <v>-0.0004804820986739594</v>
+        <v>0.01068589195845206</v>
       </c>
       <c r="AK6">
-        <v>-0.465217391304348</v>
+        <v>-0.1125945705384958</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1.06</v>
+        <v>-11.6</v>
       </c>
       <c r="AQ6">
-        <v>-0</v>
+        <v>0.7275862068965517</v>
       </c>
     </row>
     <row r="7">
@@ -1147,7 +1159,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oxbridge Acquisition Corp. (NasdaqCM:OXAC)</t>
+          <t>Patria Latin American Opportunity Acquisition Corp. (NasdaqGM:PLAO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1156,16 +1168,16 @@
         </is>
       </c>
       <c r="K7">
-        <v>-1.14</v>
+        <v>11.6</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>65.2</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.2595541401273885</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.620689655172415</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1174,37 +1186,31 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>65.2</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>0.279</v>
+        <v>0.182</v>
       </c>
       <c r="V7">
-        <v>0.001842800528401585</v>
+        <v>0.0007245222929936306</v>
       </c>
       <c r="W7">
-        <v>-0.228</v>
+        <v>-1</v>
       </c>
       <c r="X7">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y7">
-        <v>-0.3063413436811104</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>-0.06493207460280911</v>
+        <v>-1.066788527350412</v>
       </c>
       <c r="AB7">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1432734182839195</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1216,28 +1222,25 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.279</v>
+        <v>-0.182</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7">
-        <v>-0.001846202711734306</v>
+        <v>-0.0007250476061477662</v>
       </c>
       <c r="AK7">
-        <v>-0.05909764880321966</v>
+        <v>0.01657257330176653</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.495</v>
-      </c>
-      <c r="AQ7">
-        <v>0.5696969696969697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1248,7 +1251,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Patria Latin American Opportunity Acquisition Corp. (NasdaqGM:PLAO)</t>
+          <t>Investcorp India Acquisition Corp (NasdaqGM:IVCA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1257,16 +1260,16 @@
         </is>
       </c>
       <c r="K8">
-        <v>5.07</v>
+        <v>9.98</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>172.8</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.9669837716843873</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>17.31462925851703</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1278,34 +1281,28 @@
         <v>-0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>172.8</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>0.8070000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="V8">
-        <v>0.002714429868819374</v>
+        <v>0.0001678791270285394</v>
       </c>
       <c r="W8">
-        <v>-211.25</v>
+        <v>-7.560606060606061</v>
       </c>
       <c r="X8">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y8">
-        <v>-211.3283413436811</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>-5.628571428571428</v>
+        <v>-7.627394587956473</v>
       </c>
       <c r="AB8">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC8">
-        <v>-5.706912772252538</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1317,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-0.8070000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1326,16 +1323,19 @@
         <v>-0</v>
       </c>
       <c r="AJ8">
-        <v>-0.002721818053040038</v>
+        <v>-0.0001679073151620306</v>
       </c>
       <c r="AK8">
-        <v>0.06504392681550737</v>
+        <v>0.01204819277108434</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-10.9</v>
+      </c>
+      <c r="AQ8">
+        <v>0.1660550458715596</v>
       </c>
     </row>
     <row r="9">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="K9">
-        <v>6.9</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>149.8</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.907878787878788</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>17.85458879618594</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1376,67 +1376,61 @@
         <v>-0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>149.8</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>0.327</v>
+        <v>0.325</v>
       </c>
       <c r="V9">
-        <v>0.001098421229425596</v>
+        <v>0.00196969696969697</v>
       </c>
       <c r="W9">
-        <v>-575</v>
+        <v>-0.9240088105726872</v>
       </c>
       <c r="X9">
-        <v>0.0783413436811104</v>
+        <v>0.06695510149500639</v>
       </c>
       <c r="Y9">
-        <v>-575.0783413436811</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>-7.108108108108108</v>
+        <v>-0.9909639120676936</v>
       </c>
       <c r="AB9">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC9">
-        <v>-7.186449451789218</v>
+        <v>0.06686409795034959</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.982</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.982</v>
       </c>
       <c r="AG9">
-        <v>-0.327</v>
+        <v>0.657</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.005916304177561422</v>
       </c>
       <c r="AI9">
-        <v>-0</v>
+        <v>-0.2311676082862524</v>
       </c>
       <c r="AJ9">
-        <v>-0.001099629085357447</v>
+        <v>0.003966026186638657</v>
       </c>
       <c r="AK9">
-        <v>0.03476134793239077</v>
+        <v>-0.1436693636562432</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1.54</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="AQ9">
-        <v>0.5123376623376623</v>
+        <v>0.1364678899082569</v>
       </c>
     </row>
     <row r="10">
@@ -1447,7 +1441,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ahren Acquisition Corp. (NasdaqGM:AHRN)</t>
+          <t>Blockchain Coinvestors Acquisition Corp. I (NasdaqGM:BCSA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1456,16 +1450,16 @@
         </is>
       </c>
       <c r="K10">
-        <v>7.9</v>
+        <v>1.74</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>274.2</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>1.878082191780822</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>157.5862068965517</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1477,64 +1471,61 @@
         <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>274.2</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0.912</v>
+        <v>0.222</v>
       </c>
       <c r="V10">
-        <v>0.002376237623762376</v>
+        <v>0.00152054794520548</v>
       </c>
       <c r="W10">
-        <v>1128.571428571429</v>
+        <v>-0.1144736842105263</v>
       </c>
       <c r="X10">
-        <v>0.0783413436811104</v>
+        <v>0.06712784031897504</v>
       </c>
       <c r="Y10">
-        <v>1128.493087227748</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>-19.81818181818182</v>
+        <v>-0.1816015245295013</v>
       </c>
       <c r="AB10">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC10">
-        <v>-19.89652316186293</v>
+        <v>0.06694152662389057</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
-        <v>-0.912</v>
+        <v>1.548</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.01197807403397171</v>
       </c>
       <c r="AI10">
-        <v>-0</v>
+        <v>-0.1027278003482298</v>
       </c>
       <c r="AJ10">
-        <v>-0.002381897578404128</v>
+        <v>0.01049150107083796</v>
       </c>
       <c r="AK10">
-        <v>0.0641711229946524</v>
+        <v>-0.0887004354801742</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-5.57</v>
+      </c>
+      <c r="AQ10">
+        <v>0.7001795332136445</v>
       </c>
     </row>
     <row r="11">
@@ -1545,7 +1536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Target Global Acquisition I Corp. (NasdaqGM:TGAA)</t>
+          <t>Pegasus Digital Mobility Acquisition Corp. (NYSE:PGSS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1554,16 +1545,16 @@
         </is>
       </c>
       <c r="K11">
-        <v>0.03</v>
+        <v>2.35</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>183.9</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>1.566439522998296</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>78.25531914893617</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1575,67 +1566,61 @@
         <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>183.9</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>0.308</v>
+        <v>0.356</v>
       </c>
       <c r="V11">
-        <v>0.001119592875318066</v>
+        <v>0.003032367972742759</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>-0.2008547008547009</v>
       </c>
       <c r="X11">
-        <v>0.0783413436811104</v>
+        <v>0.06827139481309974</v>
       </c>
       <c r="Y11">
-        <v>1.92165865631889</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>-29.76190476190477</v>
+        <v>-0.2691260956678006</v>
       </c>
       <c r="AB11">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC11">
-        <v>-29.84024610558588</v>
+        <v>0.06743122101814406</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AG11">
-        <v>-0.308</v>
+        <v>5.864</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.05031548293156447</v>
       </c>
       <c r="AI11">
-        <v>-0</v>
+        <v>-0.8428184281842819</v>
       </c>
       <c r="AJ11">
-        <v>-0.001120847768493988</v>
+        <v>0.04757268951194184</v>
       </c>
       <c r="AK11">
-        <v>0.03812824956672444</v>
+        <v>-0.7580144777662875</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1.19</v>
+        <v>-4.93</v>
       </c>
       <c r="AQ11">
-        <v>1.050420168067227</v>
+        <v>1.174442190669371</v>
       </c>
     </row>
     <row r="12">
@@ -1646,7 +1631,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blockchain Coinvestors Acquisition Corp. I (NasdaqGM:BCSA)</t>
+          <t>Target Global Acquisition I Corp. (NasdaqGM:TGAA)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1655,16 +1640,16 @@
         </is>
       </c>
       <c r="K12">
-        <v>7.67</v>
+        <v>5.58</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>179</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>1.639194139194139</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>32.07885304659498</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1676,67 +1661,61 @@
         <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>179</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.08500000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V12">
-        <v>0.0002008981328291184</v>
+        <v>0.0006318681318681319</v>
       </c>
       <c r="W12">
-        <v>383.5</v>
+        <v>-0.7181467181467182</v>
       </c>
       <c r="X12">
-        <v>0.07835723124534058</v>
+        <v>0.06712428715653855</v>
       </c>
       <c r="Y12">
-        <v>383.4216427687547</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>-35.84905660377358</v>
+        <v>-0.7852710053032567</v>
       </c>
       <c r="AB12">
-        <v>0.0783523220392105</v>
-      </c>
-      <c r="AC12">
-        <v>-35.92740892581278</v>
+        <v>0.06704047834679867</v>
       </c>
       <c r="AD12">
-        <v>0.17</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.17</v>
+        <v>1.31</v>
       </c>
       <c r="AG12">
-        <v>0.08500000000000001</v>
+        <v>1.241</v>
       </c>
       <c r="AH12">
-        <v>0.0004016348902591726</v>
+        <v>0.01185413084788707</v>
       </c>
       <c r="AI12">
-        <v>-0.01131071190951431</v>
+        <v>-0.2943820224719102</v>
       </c>
       <c r="AJ12">
-        <v>0.0002008577808759762</v>
+        <v>0.01123676895355892</v>
       </c>
       <c r="AK12">
-        <v>-0.005623552762156799</v>
+        <v>-0.2746182783801726</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1.68</v>
+        <v>-6.97</v>
       </c>
       <c r="AQ12">
-        <v>2.261904761904762</v>
+        <v>0.1994261119081779</v>
       </c>
     </row>
     <row r="13">
@@ -1747,7 +1726,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Healthcare AI Acquisition Corp. (NasdaqGM:HAIA)</t>
+          <t>Iris Acquisition Corp (NasdaqCM:IRAA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1756,16 +1735,16 @@
         </is>
       </c>
       <c r="K13">
-        <v>21.4</v>
+        <v>2.31</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>264.3</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>3.500662251655629</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>114.4155844155844</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -1777,67 +1756,61 @@
         <v>-0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>264.3</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.465</v>
+        <v>0.115</v>
       </c>
       <c r="V13">
-        <v>0.001681735985533454</v>
+        <v>0.00152317880794702</v>
       </c>
       <c r="W13">
-        <v>2675</v>
+        <v>-0.1736842105263158</v>
       </c>
       <c r="X13">
-        <v>0.0783413436811104</v>
+        <v>0.06734088371798948</v>
       </c>
       <c r="Y13">
-        <v>2674.921658656318</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>-43.11111111111111</v>
+        <v>-0.2410250942443052</v>
       </c>
       <c r="AB13">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AC13">
-        <v>-43.18945245479222</v>
+        <v>0.06719986485800881</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>-0.465</v>
+        <v>1.375</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.01935316274840889</v>
       </c>
       <c r="AI13">
-        <v>-0</v>
+        <v>-0.1191047162270184</v>
       </c>
       <c r="AJ13">
-        <v>-0.001684568985817016</v>
+        <v>0.01788617886178862</v>
       </c>
       <c r="AK13">
-        <v>0.04447632711621234</v>
+        <v>-0.1089108910891089</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1.28</v>
+        <v>-2.99</v>
       </c>
       <c r="AQ13">
-        <v>3.03125</v>
+        <v>0.9498327759197324</v>
       </c>
     </row>
     <row r="14">
@@ -1848,7 +1821,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Investcorp Europe Acquisition Corp I (NasdaqGM:IVCB)</t>
+          <t>Healthcare AI Acquisition Corp. (NasdaqCM:HAIA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1857,7 +1830,7 @@
         </is>
       </c>
       <c r="K14">
-        <v>25.1</v>
+        <v>7.14</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -1881,954 +1854,58 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.578</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.00130121566861774</v>
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>-0.7147147147147147</v>
       </c>
       <c r="X14">
-        <v>0.0783413436811104</v>
+        <v>0.06688483196064979</v>
+      </c>
+      <c r="Y14">
+        <v>-0.7815995466753645</v>
       </c>
       <c r="AB14">
-        <v>0.0783413436811104</v>
+        <v>0.06686140957357097</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="AG14">
-        <v>-0.578</v>
+        <v>0.224</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.003429061294470639</v>
       </c>
       <c r="AI14">
-        <v>-0</v>
+        <v>-0.1937716262975779</v>
       </c>
       <c r="AJ14">
-        <v>-0.001302911036873735</v>
+        <v>0.003429061294470639</v>
       </c>
       <c r="AK14">
-        <v>0.03992264124879127</v>
+        <v>-0.1937716262975779</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AM14">
-        <v>-2.1</v>
+        <v>1.43</v>
+      </c>
+      <c r="AO14">
+        <v>-0.8671328671328672</v>
       </c>
       <c r="AQ14">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Levere Holdings Corp. (NasdaqCM:LVRA)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K15">
-        <v>11.4</v>
-      </c>
-      <c r="M15">
-        <v>-0</v>
-      </c>
-      <c r="N15">
-        <v>-0</v>
-      </c>
-      <c r="O15">
-        <v>-0</v>
-      </c>
-      <c r="P15">
-        <v>-0</v>
-      </c>
-      <c r="Q15">
-        <v>-0</v>
-      </c>
-      <c r="R15">
-        <v>-0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0.513</v>
-      </c>
-      <c r="V15">
-        <v>0.001500877706260971</v>
-      </c>
-      <c r="W15">
-        <v>-0.5507246376811594</v>
-      </c>
-      <c r="X15">
-        <v>0.07845240187284203</v>
-      </c>
-      <c r="Y15">
-        <v>-0.6291770395540015</v>
-      </c>
-      <c r="AB15">
-        <v>0.07841790106044128</v>
-      </c>
-      <c r="AD15">
-        <v>0.96</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0.96</v>
-      </c>
-      <c r="AG15">
-        <v>0.447</v>
-      </c>
-      <c r="AH15">
-        <v>0.002800793558174816</v>
-      </c>
-      <c r="AI15">
-        <v>-0.09958506224066389</v>
-      </c>
-      <c r="AJ15">
-        <v>0.001306074267999427</v>
-      </c>
-      <c r="AK15">
-        <v>-0.04402639613907219</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1.64</v>
-      </c>
-      <c r="AQ15">
-        <v>0.9024390243902439</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rocket Internet Growth Opportunities Corp. (NYSE:RKTA)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K16">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>-0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>-0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0.421</v>
-      </c>
-      <c r="V16">
-        <v>0.001248887570453871</v>
-      </c>
-      <c r="W16">
-        <v>-0.539080459770115</v>
-      </c>
-      <c r="X16">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="Y16">
-        <v>-0.6174218034512253</v>
-      </c>
-      <c r="AB16">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>-0.421</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>-0</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.0012504492409684</v>
-      </c>
-      <c r="AK16">
-        <v>0.03963845212315225</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1.62</v>
-      </c>
-      <c r="AQ16">
-        <v>0.7469135802469135</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Investcorp India Acquisition Corp (NasdaqGM:IVCA)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K17">
-        <v>3.57</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>-0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>-0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0.858</v>
-      </c>
-      <c r="V17">
-        <v>0.002565789473684211</v>
-      </c>
-      <c r="X17">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AB17">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>-0.858</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>-0</v>
-      </c>
-      <c r="AJ17">
-        <v>-0.00257238968405778</v>
-      </c>
-      <c r="AK17">
-        <v>0.3939393939393939</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1.47</v>
-      </c>
-      <c r="AQ17">
-        <v>0.5394557823129252</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Valor Latitude Acquisition Corp. (NasdaqCM:VLAT)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K18">
-        <v>9.56</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>-0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>-0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0.2</v>
-      </c>
-      <c r="V18">
-        <v>0.0006915629322268327</v>
-      </c>
-      <c r="W18">
-        <v>-0.5590643274853802</v>
-      </c>
-      <c r="X18">
-        <v>0.07835747742438279</v>
-      </c>
-      <c r="Y18">
-        <v>-0.637421804909763</v>
-      </c>
-      <c r="AB18">
-        <v>0.07835249208034173</v>
-      </c>
-      <c r="AD18">
-        <v>0.118</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0.118</v>
-      </c>
-      <c r="AG18">
-        <v>-0.08200000000000002</v>
-      </c>
-      <c r="AH18">
-        <v>0.0004078557158559094</v>
-      </c>
-      <c r="AI18">
-        <v>-0.01271277741865977</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.0002836212204013587</v>
-      </c>
-      <c r="AK18">
-        <v>0.008647964564437883</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1.38</v>
-      </c>
-      <c r="AQ18">
-        <v>0.7536231884057972</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>World Quantum Growth Acquisition Corp. (NYSE:WQGA)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K19">
-        <v>13.8</v>
-      </c>
-      <c r="M19">
-        <v>-0</v>
-      </c>
-      <c r="N19">
-        <v>-0</v>
-      </c>
-      <c r="O19">
-        <v>-0</v>
-      </c>
-      <c r="P19">
-        <v>-0</v>
-      </c>
-      <c r="Q19">
-        <v>-0</v>
-      </c>
-      <c r="R19">
-        <v>-0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0.203</v>
-      </c>
-      <c r="V19">
-        <v>0.0007813702848344881</v>
-      </c>
-      <c r="W19">
-        <v>-0.7709497206703911</v>
-      </c>
-      <c r="X19">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="Y19">
-        <v>-0.8492910643515015</v>
-      </c>
-      <c r="AB19">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>-0.203</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>-0</v>
-      </c>
-      <c r="AJ19">
-        <v>-0.0007819813017870006</v>
-      </c>
-      <c r="AK19">
-        <v>0.02523933855526545</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1.26</v>
-      </c>
-      <c r="AQ19">
-        <v>1.007936507936508</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TB SA Acquisition Corp (NasdaqCM:TBSA)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K20">
-        <v>4.37</v>
-      </c>
-      <c r="M20">
-        <v>-0</v>
-      </c>
-      <c r="N20">
-        <v>-0</v>
-      </c>
-      <c r="O20">
-        <v>-0</v>
-      </c>
-      <c r="P20">
-        <v>-0</v>
-      </c>
-      <c r="Q20">
-        <v>-0</v>
-      </c>
-      <c r="R20">
-        <v>-0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0.047</v>
-      </c>
-      <c r="V20">
-        <v>0.0001865079365079365</v>
-      </c>
-      <c r="W20">
-        <v>-0.7105691056910569</v>
-      </c>
-      <c r="X20">
-        <v>0.07842262310978824</v>
-      </c>
-      <c r="Y20">
-        <v>-0.7889917288008451</v>
-      </c>
-      <c r="AB20">
-        <v>0.0783738249390547</v>
-      </c>
-      <c r="AD20">
-        <v>0.518</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0.518</v>
-      </c>
-      <c r="AG20">
-        <v>0.471</v>
-      </c>
-      <c r="AH20">
-        <v>0.002051338914453623</v>
-      </c>
-      <c r="AI20">
-        <v>-0.2070343725019984</v>
-      </c>
-      <c r="AJ20">
-        <v>0.001865560797081645</v>
-      </c>
-      <c r="AK20">
-        <v>-0.1847783444488035</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1.2</v>
-      </c>
-      <c r="AQ20">
-        <v>2.933333333333334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Blue Whale Acquisition Corp I (NasdaqCM:BWC)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K21">
-        <v>4.35</v>
-      </c>
-      <c r="M21">
-        <v>-0</v>
-      </c>
-      <c r="N21">
-        <v>-0</v>
-      </c>
-      <c r="O21">
-        <v>-0</v>
-      </c>
-      <c r="P21">
-        <v>-0</v>
-      </c>
-      <c r="Q21">
-        <v>-0</v>
-      </c>
-      <c r="R21">
-        <v>-0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>2.13</v>
-      </c>
-      <c r="V21">
-        <v>0.008537074148296592</v>
-      </c>
-      <c r="W21">
-        <v>-0.2939189189189189</v>
-      </c>
-      <c r="X21">
-        <v>0.07881362105253209</v>
-      </c>
-      <c r="Y21">
-        <v>-0.3727325399714509</v>
-      </c>
-      <c r="AB21">
-        <v>0.07852823309591374</v>
-      </c>
-      <c r="AD21">
-        <v>2.98</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>2.98</v>
-      </c>
-      <c r="AG21">
-        <v>0.8500000000000001</v>
-      </c>
-      <c r="AH21">
-        <v>0.01180291508238276</v>
-      </c>
-      <c r="AI21">
-        <v>-0.3539192399049881</v>
-      </c>
-      <c r="AJ21">
-        <v>0.003395246654683444</v>
-      </c>
-      <c r="AK21">
-        <v>-0.08056872037914692</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>JATT Acquisition Corp (NYSE:JATT)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K22">
-        <v>5.36</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>-0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>-0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0.074</v>
-      </c>
-      <c r="V22">
-        <v>0.0004202157864849518</v>
-      </c>
-      <c r="W22">
-        <v>-0.5203883495145631</v>
-      </c>
-      <c r="X22">
-        <v>0.07840870542503053</v>
-      </c>
-      <c r="Y22">
-        <v>-0.5987970549395937</v>
-      </c>
-      <c r="AB22">
-        <v>0.07836827254898784</v>
-      </c>
-      <c r="AD22">
-        <v>0.3</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0.3</v>
-      </c>
-      <c r="AG22">
-        <v>0.226</v>
-      </c>
-      <c r="AH22">
-        <v>0.001700680272108843</v>
-      </c>
-      <c r="AI22">
-        <v>-0.04405286343612334</v>
-      </c>
-      <c r="AJ22">
-        <v>0.001281716819981171</v>
-      </c>
-      <c r="AK22">
-        <v>-0.03282975014526437</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>-0.9</v>
-      </c>
-      <c r="AQ22">
-        <v>3.022222222222222</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Aries I Acquisition Corporation (NasdaqCM:RAM)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K23">
-        <v>2.85</v>
-      </c>
-      <c r="M23">
-        <v>123.3</v>
-      </c>
-      <c r="N23">
-        <v>2.03801652892562</v>
-      </c>
-      <c r="O23">
-        <v>43.26315789473684</v>
-      </c>
-      <c r="P23">
-        <v>-0</v>
-      </c>
-      <c r="Q23">
-        <v>-0</v>
-      </c>
-      <c r="R23">
-        <v>-0</v>
-      </c>
-      <c r="S23">
-        <v>123.3</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>0.026</v>
-      </c>
-      <c r="V23">
-        <v>0.0004297520661157025</v>
-      </c>
-      <c r="W23">
-        <v>-0.2714285714285715</v>
-      </c>
-      <c r="X23">
-        <v>0.07945895851903931</v>
-      </c>
-      <c r="Y23">
-        <v>-0.3508875299476107</v>
-      </c>
-      <c r="AB23">
-        <v>0.07877658621564496</v>
-      </c>
-      <c r="AD23">
-        <v>1.71</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>1.71</v>
-      </c>
-      <c r="AG23">
-        <v>1.684</v>
-      </c>
-      <c r="AH23">
-        <v>0.02748754219578846</v>
-      </c>
-      <c r="AI23">
-        <v>-0.3461538461538461</v>
-      </c>
-      <c r="AJ23">
-        <v>0.02708092113727004</v>
-      </c>
-      <c r="AK23">
-        <v>-0.3391059202577527</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-0.507</v>
-      </c>
-      <c r="AQ23">
-        <v>6.193293885601578</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Vertex Technology Acquisition Corporation Ltd. (SGX:VT1)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K24">
-        <v>-2.37</v>
-      </c>
-      <c r="M24">
-        <v>-0</v>
-      </c>
-      <c r="N24">
-        <v>-0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>-0</v>
-      </c>
-      <c r="Q24">
-        <v>-0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>2.56</v>
-      </c>
-      <c r="V24">
-        <v>0.1267326732673267</v>
-      </c>
-      <c r="X24">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AB24">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>-2.56</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>-0.145124716553288</v>
-      </c>
-      <c r="AK24">
-        <v>-0.1264822134387352</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
+        <v>-0.8671328671328672</v>
       </c>
     </row>
   </sheetData>
